--- a/Util/userdata.xlsx
+++ b/Util/userdata.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\karth\Project\pythonProjectTEST\Util\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3A35E260-E489-4FA5-AB6A-FBE0BECB815D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E61FAA0-1326-4B9A-82A9-8BA493F81354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{79485BA7-E2B9-4E44-A85B-1D67C785CB90}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Username</t>
   </si>
@@ -47,22 +47,10 @@
     <t>Password</t>
   </si>
   <si>
-    <t>user123@gmail.com</t>
+    <t>Password123</t>
   </si>
   <si>
-    <t>test#12345</t>
-  </si>
-  <si>
-    <t>user123@gmail</t>
-  </si>
-  <si>
-    <t>user123@hotmail.in</t>
-  </si>
-  <si>
-    <t>test#6789</t>
-  </si>
-  <si>
-    <t>test@3448</t>
+    <t>student</t>
   </si>
 </sst>
 </file>
@@ -445,11 +433,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF977279-D702-402C-91E3-188FE680258C}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -462,34 +450,15 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{04F05F2A-8E78-424D-8899-300C1362F527}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{42BDB8C6-F04F-4E36-BEA4-88CAD2E9E00E}"/>
-    <hyperlink ref="A4" r:id="rId3" xr:uid="{8F970762-1967-4831-A774-152FA25CBD15}"/>
-    <hyperlink ref="B4" r:id="rId4" xr:uid="{EFE2BB19-6241-4A53-A293-EE65C394ACFA}"/>
+    <hyperlink ref="A2" r:id="rId1" display="user123@gmail.com" xr:uid="{04F05F2A-8E78-424D-8899-300C1362F527}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
